--- a/output/laminas_comunales/comunal_m_saldomigr_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_m_saldomigr_a_2022_metropolitana.xlsx
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2018_2022. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2018_2022. Escala comunal recortada a percentiles 3-97. Sobre umbral: San Miguel (7.854); Lampa (12.458); Ñuñoa (11.201); Padre Hurtado (6.223); Buin (9.461). Bajo umbral: Independencia (-8.700); Peñalolén (-12.223); Calera de Tango (-8.272); Santiago (-25.045); Puente Alto (-26.862); San Bernardo (-6.851); Cerro Navia (-5.840); Conchalí (-5.928); El Bosque (-8.252); Estación Central (-8.586); La Granja (-6.903); La Pintana (-8.596); Lo Espejo (-6.280); Lo Prado (-6.161); Maipú (-25.871); Pedro Aguirre Cerda (-7.528); Pudahuel (-9.307); Quilicura (-10.207); Quinta Normal (-6.977); Recoleta (-13.010); Renca (-7.360).</t>
         </is>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_m_saldomigr_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_m_saldomigr_a_2022_metropolitana.xlsx
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2018_2022. Escala comunal recortada a percentiles 3-97. Sobre umbral: San Miguel (7.854); Lampa (12.458); Ñuñoa (11.201); Padre Hurtado (6.223); Buin (9.461). Bajo umbral: Independencia (-8.700); Peñalolén (-12.223); Calera de Tango (-8.272); Santiago (-25.045); Puente Alto (-26.862); San Bernardo (-6.851); Cerro Navia (-5.840); Conchalí (-5.928); El Bosque (-8.252); Estación Central (-8.586); La Granja (-6.903); La Pintana (-8.596); Lo Espejo (-6.280); Lo Prado (-6.161); Maipú (-25.871); Pedro Aguirre Cerda (-7.528); Pudahuel (-9.307); Quilicura (-10.207); Quinta Normal (-6.977); Recoleta (-13.010); Renca (-7.360).</t>
+          <t>Periodo 2018_2022. Escala comunal recortada a percentiles 3-97. Sobre umbral: San Miguel (7.854); Lampa (12.458); Ñuñoa (11.201); Padre Hurtado (6.223); Buin (9.461). Bajo umbral: Independencia (-8.700); Peñalolén (-12.223); Calera de Tango (-8.272); Santiago (-25.045); Puente Alto (-26.862); San Bernardo (-6.851); y 15 más.</t>
         </is>
       </c>
     </row>
